--- a/从零开始学Slots/从零开始学Slots-04-数值篇-1x3LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-04-数值篇-1x3LineSlots.xlsx
@@ -5106,6 +5106,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J139" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5649,5 +5652,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:T57" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-04-数值篇-1x3LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-04-数值篇-1x3LineSlots.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="138">
   <si>
     <r>
       <rPr>
@@ -4173,7 +4173,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4304,6 +4304,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5167,8 +5171,8 @@
       <c r="B5" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>91</v>
+      <c r="C5" s="33">
+        <v>1</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>

--- a/从零开始学Slots/从零开始学Slots-04-数值篇-1x3LineSlots.xlsx
+++ b/从零开始学Slots/从零开始学Slots-04-数值篇-1x3LineSlots.xlsx
@@ -3985,11 +3985,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -4173,7 +4174,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4307,6 +4308,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5442,7 +5447,7 @@
         <f aca="false">B24*C24*D24</f>
         <v>48</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F24" s="34" t="n">
         <f aca="false">E24/$B$10</f>
         <v>0.384</v>
       </c>
@@ -5474,7 +5479,7 @@
         <f aca="false">B25*C25*D25</f>
         <v>2</v>
       </c>
-      <c r="F25" s="21" t="n">
+      <c r="F25" s="34" t="n">
         <f aca="false">E25/$B$10</f>
         <v>0.016</v>
       </c>
